--- a/artfynd/A 63217-2025 artfynd.xlsx
+++ b/artfynd/A 63217-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -996,6 +996,640 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>132208885</v>
+      </c>
+      <c r="B5" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Djupsundet, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>514272</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6511571</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>132208892</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57911</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Djupsundet, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>514354</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6511484</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>132208887</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93136</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Djupsundet, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>514341</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6511532</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132208886</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93136</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Djupsundet, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>514329</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6511536</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132208894</v>
+      </c>
+      <c r="B9" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Djupsundet, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>514421</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6511466</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132208889</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93136</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Djupsundet, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>514348</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6511496</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 63217-2025 artfynd.xlsx
+++ b/artfynd/A 63217-2025 artfynd.xlsx
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132208894</v>
+        <v>132208889</v>
       </c>
       <c r="B9" t="n">
-        <v>5179</v>
+        <v>93136</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,28 +1435,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1464,10 +1466,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514421</v>
+        <v>514348</v>
       </c>
       <c r="R9" t="n">
-        <v>6511466</v>
+        <v>6511496</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1527,10 +1529,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132208889</v>
+        <v>132208894</v>
       </c>
       <c r="B10" t="n">
-        <v>93136</v>
+        <v>5179</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1538,30 +1540,28 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1569,10 +1569,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514348</v>
+        <v>514421</v>
       </c>
       <c r="R10" t="n">
-        <v>6511496</v>
+        <v>6511466</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 63217-2025 artfynd.xlsx
+++ b/artfynd/A 63217-2025 artfynd.xlsx
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132208889</v>
+        <v>132208894</v>
       </c>
       <c r="B9" t="n">
-        <v>93136</v>
+        <v>5179</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,30 +1435,28 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1466,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514348</v>
+        <v>514421</v>
       </c>
       <c r="R9" t="n">
-        <v>6511496</v>
+        <v>6511466</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,10 +1527,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132208894</v>
+        <v>132208889</v>
       </c>
       <c r="B10" t="n">
-        <v>5179</v>
+        <v>93136</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1540,28 +1538,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1569,10 +1569,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514421</v>
+        <v>514348</v>
       </c>
       <c r="R10" t="n">
-        <v>6511466</v>
+        <v>6511496</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 63217-2025 artfynd.xlsx
+++ b/artfynd/A 63217-2025 artfynd.xlsx
@@ -1112,7 +1112,7 @@
         <v>132208892</v>
       </c>
       <c r="B6" t="n">
-        <v>57911</v>
+        <v>57945</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>132208887</v>
       </c>
       <c r="B7" t="n">
-        <v>93136</v>
+        <v>93172</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>132208886</v>
       </c>
       <c r="B8" t="n">
-        <v>93136</v>
+        <v>93172</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132208894</v>
+        <v>132208889</v>
       </c>
       <c r="B9" t="n">
-        <v>5179</v>
+        <v>93172</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,28 +1435,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1464,10 +1466,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514421</v>
+        <v>514348</v>
       </c>
       <c r="R9" t="n">
-        <v>6511466</v>
+        <v>6511496</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1527,10 +1529,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132208889</v>
+        <v>132208894</v>
       </c>
       <c r="B10" t="n">
-        <v>93136</v>
+        <v>5179</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1538,30 +1540,28 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1569,10 +1569,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514348</v>
+        <v>514421</v>
       </c>
       <c r="R10" t="n">
-        <v>6511496</v>
+        <v>6511466</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 63217-2025 artfynd.xlsx
+++ b/artfynd/A 63217-2025 artfynd.xlsx
@@ -1217,7 +1217,7 @@
         <v>132208887</v>
       </c>
       <c r="B7" t="n">
-        <v>93172</v>
+        <v>93177</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>132208886</v>
       </c>
       <c r="B8" t="n">
-        <v>93172</v>
+        <v>93177</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>132208889</v>
       </c>
       <c r="B9" t="n">
-        <v>93172</v>
+        <v>93177</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 63217-2025 artfynd.xlsx
+++ b/artfynd/A 63217-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112298764</v>
+        <v>112298690</v>
       </c>
       <c r="B2" t="n">
-        <v>90855</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>1101</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514413</v>
+        <v>514431</v>
       </c>
       <c r="R2" t="n">
-        <v>6511604</v>
+        <v>6511503</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -767,6 +762,11 @@
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
       <c r="AW2" t="inlineStr">
         <is>
           <t>Magnus Wadstein</t>
@@ -781,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112298747</v>
+        <v>112298764</v>
       </c>
       <c r="B3" t="n">
-        <v>90899</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,7 +819,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514413</v>
+        <v>514412</v>
       </c>
       <c r="R3" t="n">
         <v>6511604</v>
@@ -887,15 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112298690</v>
+        <v>132208886</v>
       </c>
       <c r="B4" t="n">
-        <v>89810</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93271</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,37 +893,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1101</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>900 M NO Brahus, Ög</t>
+          <t>Djupsundet, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514432</v>
+        <v>514329</v>
       </c>
       <c r="R4" t="n">
-        <v>6511504</v>
+        <v>6511536</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,12 +954,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-08-24</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-08-24</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,51 +973,46 @@
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>Mikael Hagström</t>
-        </is>
-      </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132208885</v>
+        <v>132208887</v>
       </c>
       <c r="B5" t="n">
-        <v>8455</v>
+        <v>93271</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1033,12 +1022,6 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1046,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514272</v>
+        <v>514341</v>
       </c>
       <c r="R5" t="n">
-        <v>6511571</v>
+        <v>6511532</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132208892</v>
+        <v>132208889</v>
       </c>
       <c r="B6" t="n">
-        <v>57951</v>
+        <v>93271</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1120,31 +1103,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1152,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514354</v>
+        <v>514348</v>
       </c>
       <c r="R6" t="n">
-        <v>6511484</v>
+        <v>6511496</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,6 +1178,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1214,10 +1197,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132208887</v>
+        <v>132208892</v>
       </c>
       <c r="B7" t="n">
-        <v>93201</v>
+        <v>57972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1225,30 +1208,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1256,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514341</v>
+        <v>514354</v>
       </c>
       <c r="R7" t="n">
-        <v>6511532</v>
+        <v>6511484</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1284,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1319,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132208886</v>
+        <v>132208894</v>
       </c>
       <c r="B8" t="n">
-        <v>93201</v>
+        <v>5181</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1330,30 +1313,28 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1361,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514329</v>
+        <v>514421</v>
       </c>
       <c r="R8" t="n">
-        <v>6511536</v>
+        <v>6511466</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,10 +1405,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132208894</v>
+        <v>132208885</v>
       </c>
       <c r="B9" t="n">
-        <v>5179</v>
+        <v>8460</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,28 +1416,36 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1464,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514421</v>
+        <v>514272</v>
       </c>
       <c r="R9" t="n">
-        <v>6511466</v>
+        <v>6511571</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,111 +1513,6 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>132208889</v>
-      </c>
-      <c r="B10" t="n">
-        <v>93201</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Djupsundet, Ög</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>514348</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6511496</v>
-      </c>
-      <c r="S10" t="n">
-        <v>10</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Motala</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Godegård</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Emil Lindgren</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Emil Lindgren</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63217-2025 artfynd.xlsx
+++ b/artfynd/A 63217-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1197,53 +1197,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132208892</v>
+        <v>134665323</v>
       </c>
       <c r="B7" t="n">
-        <v>57972</v>
+        <v>91995</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Djupsundet, Ög</t>
+          <t>Isefall, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514354</v>
+        <v>514351</v>
       </c>
       <c r="R7" t="n">
-        <v>6511484</v>
+        <v>6511661</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,12 +1262,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1290,22 +1287,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132208894</v>
+        <v>132208892</v>
       </c>
       <c r="B8" t="n">
-        <v>5181</v>
+        <v>57972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1313,28 +1310,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514421</v>
+        <v>514354</v>
       </c>
       <c r="R8" t="n">
-        <v>6511466</v>
+        <v>6511484</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,7 +1386,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1405,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132208885</v>
+        <v>132208894</v>
       </c>
       <c r="B9" t="n">
-        <v>8460</v>
+        <v>5181</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1416,36 +1415,28 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1453,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514272</v>
+        <v>514421</v>
       </c>
       <c r="R9" t="n">
-        <v>6511571</v>
+        <v>6511466</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,6 +1504,117 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132208885</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Djupsundet, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>514272</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6511571</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
